--- a/外務支出總表 - 假日2.xlsx
+++ b/外務支出總表 - 假日2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F99E66-BE28-4535-9E0A-B2A350113E7E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11120BD0-A478-455D-8537-DB1B61C9E585}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" tabRatio="749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,9 +85,6 @@
     <t>總計</t>
   </si>
   <si>
-    <t>經理簽章：</t>
-  </si>
-  <si>
     <t>人員編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +220,10 @@
   </si>
   <si>
     <t>劉彥璋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經理簽章：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -330,7 +331,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -393,62 +394,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -499,11 +448,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -514,131 +483,114 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -937,7 +889,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="24.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
@@ -951,633 +903,660 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="7" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+    </row>
+    <row r="4" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
+        <v>21094053</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="49.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="14">
-        <v>21094053</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17">
-        <f>D3-F3</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19">
-        <f>E3*30+F3*10</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="20"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="21">
-        <v>20298022</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="17">
-        <f t="shared" ref="E4:E26" si="0">D4-F4</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="19">
-        <f t="shared" ref="G4:G26" si="1">E4*30+F4*10</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="25"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6">
+        <f>D4-F4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8">
+        <f>E4*30+F4*10</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="40"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="21">
-        <v>20260601</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="25"/>
+      <c r="A5" s="9">
+        <v>20298022</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6">
+        <f t="shared" ref="E5:E27" si="0">D5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="8">
+        <f t="shared" ref="G5:G27" si="1">E5*30+F5*10</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="13"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="21">
+      <c r="A6" s="9">
+        <v>20260601</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="9">
         <v>21002102</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="24"/>
-      <c r="G6" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="25"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="21">
+      <c r="C7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="9">
         <v>20903101</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="25"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="21">
+      <c r="B8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="9">
         <v>20296012</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="25"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="21">
-        <v>20251027</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="25"/>
+      <c r="C9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="13"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="21">
-        <v>20260602</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="25"/>
+      <c r="A10" s="9">
+        <v>20251027</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="13"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="21">
-        <v>20220418</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="25"/>
+      <c r="A11" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="21">
-        <v>20251117</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="24"/>
-      <c r="G12" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="25"/>
+      <c r="A12" s="9">
+        <v>20220418</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="21">
-        <v>21192074</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="25"/>
+      <c r="A13" s="9">
+        <v>20251117</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="13"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="21">
-        <v>20240513</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="25"/>
+      <c r="A14" s="9">
+        <v>21192074</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="13"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="21">
-        <v>20250324</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="25"/>
+      <c r="A15" s="9">
+        <v>20240513</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="13"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="21">
-        <v>20250825</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="25"/>
+      <c r="A16" s="9">
+        <v>20250324</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="13"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="21">
-        <v>20290022</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="25"/>
+    <row r="17" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="9">
+        <v>20250825</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="13"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="21">
-        <v>20200103</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="25"/>
+    <row r="18" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="9">
+        <v>20290022</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="13"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="21">
-        <v>260604</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="25"/>
+    <row r="19" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="9">
+        <v>20200103</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="13"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="21">
-        <v>20260305</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="25"/>
+    <row r="20" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="9">
+        <v>260604</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="13"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="21">
+    <row r="21" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="9">
+        <v>20260305</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="9">
         <v>20296021</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B22" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="9">
+        <v>21005222</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="25"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="21">
-        <v>21005222</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="25"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="40">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="20">
         <v>20289041</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B24" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="24"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="20">
+        <v>260603</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="G25" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="24"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" s="3" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="20">
+        <v>20240710</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="24"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" s="3" customFormat="1" ht="49.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="20">
+        <v>20200103</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="44"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="40">
-        <v>260603</v>
-      </c>
-      <c r="B24" s="40" t="s">
+      <c r="C27" s="20"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="G27" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="27"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" s="3" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="15">
+        <f>SUM(D4:D26)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="16">
+        <f>SUM(E4:E26)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="17">
+        <f>SUM(F4:F26)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="18">
+        <f>SUM(G4:G26)</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="19"/>
+    </row>
+    <row r="30" spans="1:11" ht="61.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="44"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" s="3" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="40">
-        <v>20240710</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="43"/>
-      <c r="G25" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="44"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" s="3" customFormat="1" ht="49.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="27">
-        <v>20200103</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:12" ht="49.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="31">
-        <f>SUM(D3:D25)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="32">
-        <f>SUM(E3:E25)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="33">
-        <f>SUM(F3:F25)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="34">
-        <f>SUM(G3:G25)</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="35"/>
-    </row>
-    <row r="28" spans="1:12" ht="61.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="L31" s="3"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+    </row>
+    <row r="33" spans="12:12" x14ac:dyDescent="0.45">
+      <c r="L33" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.51181102362204722" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="59" fitToWidth="0" orientation="portrait" r:id="rId1"/>

--- a/外務支出總表 - 假日2.xlsx
+++ b/外務支出總表 - 假日2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11120BD0-A478-455D-8537-DB1B61C9E585}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9093027-50B8-40B4-9174-0402DD844BF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" tabRatio="749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,6 +564,19 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -578,19 +591,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -904,18 +904,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="27" t="s">
@@ -924,13 +924,13 @@
       <c r="B2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="32" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="33" t="s">
         <v>34</v>
       </c>
       <c r="F2" s="23" t="s">
@@ -973,7 +973,7 @@
         <f>E4*30+F4*10</f>
         <v>0</v>
       </c>
-      <c r="H4" s="40"/>
+      <c r="H4" s="34"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
@@ -1513,39 +1513,39 @@
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="33"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="38"/>
       <c r="D29" s="15">
-        <f>SUM(D4:D26)</f>
+        <f>SUM(D4:D27)</f>
         <v>0</v>
       </c>
       <c r="E29" s="16">
-        <f>SUM(E4:E26)</f>
+        <f>SUM(E4:E27)</f>
         <v>0</v>
       </c>
       <c r="F29" s="17">
-        <f>SUM(F4:F26)</f>
+        <f>SUM(F4:F27)</f>
         <v>0</v>
       </c>
       <c r="G29" s="18">
-        <f>SUM(G4:G26)</f>
+        <f>SUM(G4:G27)</f>
         <v>0</v>
       </c>
       <c r="H29" s="19"/>
     </row>
     <row r="30" spans="1:11" ht="61.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
     </row>
     <row r="33" spans="12:12" x14ac:dyDescent="0.45">
       <c r="L33" s="3"/>
